--- a/03_Group_comparisons/Proteome_T3/c_data/05_module_classification.xlsx
+++ b/03_Group_comparisons/Proteome_T3/c_data/05_module_classification.xlsx
@@ -310,7 +310,7 @@
     <t>03_Group_comparisons/Proteome_T3/c_data/01_design.rds</t>
   </si>
   <si>
-    <t>5b6aabc2a465a28cbc3adbf8fd2c32aa</t>
+    <t>2bc130dc3f17c8c4cba1b5d71f9a0a1f</t>
   </si>
   <si>
     <t>modules</t>
@@ -319,7 +319,7 @@
     <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
   </si>
   <si>
-    <t>9062a97ff96fac52908895e0eeb7bf57</t>
+    <t>37335a295505b53dcf355baf87333202</t>
   </si>
   <si>
     <t>BiocGenerics</t>
